--- a/Data/ECON_경제활동인구_KK.xlsx
+++ b/Data/ECON_경제활동인구_KK.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\내 드라이브\Research\SavedData\KorailEconNews\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DataScience\Lecture\특강_20250412_한국지능정보사회진흥원_빅데이터센터\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{181AF0AA-1703-4EEA-AB5D-7D26657A5047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B859B586-6303-4948-A771-9C8968AB8CCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24098" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="데이터" sheetId="1" r:id="rId1"/>
@@ -608,7 +608,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="#,##0.0_ "/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -618,11 +618,15 @@
       <sz val="10.5"/>
       <color rgb="FF555555"/>
       <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color rgb="FF888282"/>
       <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="8"/>
@@ -722,6 +726,9 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -729,9 +736,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1069,207 +1073,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y130"/>
-  <sheetFormatPr defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="25" width="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="23.25" customHeight="1">
+    <row r="1" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="7"/>
-    </row>
-    <row r="2" spans="1:25" ht="23.25" customHeight="1">
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="7"/>
+      <c r="S1" s="7"/>
+      <c r="T1" s="7"/>
+      <c r="U1" s="7"/>
+      <c r="V1" s="7"/>
+      <c r="W1" s="7"/>
+      <c r="X1" s="7"/>
+      <c r="Y1" s="8"/>
+    </row>
+    <row r="2" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="5" t="s">
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="5" t="s">
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="5" t="s">
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="5" t="s">
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="7"/>
-      <c r="V2" s="5" t="s">
+      <c r="S2" s="7"/>
+      <c r="T2" s="7"/>
+      <c r="U2" s="8"/>
+      <c r="V2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="W2" s="6"/>
-      <c r="X2" s="6"/>
-      <c r="Y2" s="7"/>
-    </row>
-    <row r="3" spans="1:25" ht="23.25" customHeight="1">
+      <c r="W2" s="7"/>
+      <c r="X2" s="7"/>
+      <c r="Y2" s="8"/>
+    </row>
+    <row r="3" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7" t="s">
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7" t="s">
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7" t="s">
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7" t="s">
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="7"/>
-      <c r="V3" s="7" t="s">
+      <c r="S3" s="8"/>
+      <c r="T3" s="8"/>
+      <c r="U3" s="8"/>
+      <c r="V3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="W3" s="7"/>
-      <c r="X3" s="7"/>
-      <c r="Y3" s="7"/>
-    </row>
-    <row r="4" spans="1:25" ht="23.25" customHeight="1">
+      <c r="W3" s="8"/>
+      <c r="X3" s="8"/>
+      <c r="Y3" s="8"/>
+    </row>
+    <row r="4" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="5" t="s">
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="5" t="s">
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="5" t="s">
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="5" t="s">
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="8"/>
+      <c r="R4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="5" t="s">
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="8"/>
+      <c r="V4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="7"/>
-    </row>
-    <row r="5" spans="1:25" ht="23.25" customHeight="1">
+      <c r="W4" s="7"/>
+      <c r="X4" s="7"/>
+      <c r="Y4" s="8"/>
+    </row>
+    <row r="5" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="5" t="s">
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="5" t="s">
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="5" t="s">
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="5" t="s">
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="S5" s="6"/>
-      <c r="T5" s="6"/>
-      <c r="U5" s="7"/>
-      <c r="V5" s="5" t="s">
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="8"/>
+      <c r="V5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="W5" s="6"/>
-      <c r="X5" s="6"/>
-      <c r="Y5" s="7"/>
-    </row>
-    <row r="6" spans="1:25" ht="23.25" customHeight="1">
+      <c r="W5" s="7"/>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="8"/>
+    </row>
+    <row r="6" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>20</v>
       </c>
@@ -1346,7 +1350,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="23.25" customHeight="1">
+    <row r="7" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>24</v>
       </c>
@@ -1423,108 +1427,108 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="23.25" customHeight="1">
-      <c r="A8" s="8" t="s">
+    <row r="8" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="B8" s="8" t="str">
+      <c r="B8" s="5" t="str">
         <f>$B$3&amp;"_"&amp;B7</f>
         <v>경제활동인구_원자료</v>
       </c>
-      <c r="C8" s="8" t="str">
+      <c r="C8" s="5" t="str">
         <f t="shared" ref="C8:E8" si="0">$B$3&amp;"_"&amp;C7</f>
         <v>경제활동인구_전기대비증감</v>
       </c>
-      <c r="D8" s="8" t="str">
+      <c r="D8" s="5" t="str">
         <f t="shared" si="0"/>
         <v>경제활동인구_전년동기대비증감</v>
       </c>
-      <c r="E8" s="8" t="str">
+      <c r="E8" s="5" t="str">
         <f t="shared" si="0"/>
         <v>경제활동인구_이동평균(3기간)</v>
       </c>
-      <c r="F8" s="8" t="str">
+      <c r="F8" s="5" t="str">
         <f>$F$3&amp;"_"&amp;F7</f>
         <v xml:space="preserve">  실업률_원자료</v>
       </c>
-      <c r="G8" s="8" t="str">
+      <c r="G8" s="5" t="str">
         <f t="shared" ref="G8:I8" si="1">$F$3&amp;"_"&amp;G7</f>
         <v xml:space="preserve">  실업률_전기대비증감</v>
       </c>
-      <c r="H8" s="8" t="str">
+      <c r="H8" s="5" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">  실업률_전년동기대비증감</v>
       </c>
-      <c r="I8" s="8" t="str">
+      <c r="I8" s="5" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">  실업률_이동평균(3기간)</v>
       </c>
-      <c r="J8" s="8" t="str">
+      <c r="J8" s="5" t="str">
         <f>$J$3&amp;"_"&amp;J7</f>
         <v>15세이상인구_원자료</v>
       </c>
-      <c r="K8" s="8" t="str">
+      <c r="K8" s="5" t="str">
         <f t="shared" ref="K8:M8" si="2">$J$3&amp;"_"&amp;K7</f>
         <v>15세이상인구_전기대비증감</v>
       </c>
-      <c r="L8" s="8" t="str">
+      <c r="L8" s="5" t="str">
         <f t="shared" si="2"/>
         <v>15세이상인구_전년동기대비증감</v>
       </c>
-      <c r="M8" s="8" t="str">
+      <c r="M8" s="5" t="str">
         <f t="shared" si="2"/>
         <v>15세이상인구_이동평균(3기간)</v>
       </c>
-      <c r="N8" s="8" t="str">
+      <c r="N8" s="5" t="str">
         <f>$N$3&amp;"_"&amp;N7</f>
         <v>비경제활동인구_원자료</v>
       </c>
-      <c r="O8" s="8" t="str">
+      <c r="O8" s="5" t="str">
         <f t="shared" ref="O8:Q8" si="3">$N$3&amp;"_"&amp;O7</f>
         <v>비경제활동인구_전기대비증감</v>
       </c>
-      <c r="P8" s="8" t="str">
+      <c r="P8" s="5" t="str">
         <f t="shared" si="3"/>
         <v>비경제활동인구_전년동기대비증감</v>
       </c>
-      <c r="Q8" s="8" t="str">
+      <c r="Q8" s="5" t="str">
         <f t="shared" si="3"/>
         <v>비경제활동인구_이동평균(3기간)</v>
       </c>
-      <c r="R8" s="8" t="str">
+      <c r="R8" s="5" t="str">
         <f>$R$3&amp;"_"&amp;R7</f>
         <v>경제활동참가율_원자료</v>
       </c>
-      <c r="S8" s="8" t="str">
+      <c r="S8" s="5" t="str">
         <f t="shared" ref="S8:U8" si="4">$R$3&amp;"_"&amp;S7</f>
         <v>경제활동참가율_전기대비증감</v>
       </c>
-      <c r="T8" s="8" t="str">
+      <c r="T8" s="5" t="str">
         <f t="shared" si="4"/>
         <v>경제활동참가율_전년동기대비증감</v>
       </c>
-      <c r="U8" s="8" t="str">
+      <c r="U8" s="5" t="str">
         <f t="shared" si="4"/>
         <v>경제활동참가율_이동평균(3기간)</v>
       </c>
-      <c r="V8" s="8" t="str">
+      <c r="V8" s="5" t="str">
         <f>$V$3&amp;"_"&amp;V7</f>
         <v>고용률_원자료</v>
       </c>
-      <c r="W8" s="8" t="str">
+      <c r="W8" s="5" t="str">
         <f t="shared" ref="W8:Y8" si="5">$V$3&amp;"_"&amp;W7</f>
         <v>고용률_전기대비증감</v>
       </c>
-      <c r="X8" s="8" t="str">
+      <c r="X8" s="5" t="str">
         <f t="shared" si="5"/>
         <v>고용률_전년동기대비증감</v>
       </c>
-      <c r="Y8" s="8" t="str">
+      <c r="Y8" s="5" t="str">
         <f t="shared" si="5"/>
         <v>고용률_이동평균(3기간)</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="23.25" customHeight="1">
+    <row r="9" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>29</v>
       </c>
@@ -1601,7 +1605,7 @@
         <v>59.3</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="23.25" customHeight="1">
+    <row r="10" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>30</v>
       </c>
@@ -1678,7 +1682,7 @@
         <v>59.3</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="23.25" customHeight="1">
+    <row r="11" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>31</v>
       </c>
@@ -1755,7 +1759,7 @@
         <v>59.8</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="23.25" customHeight="1">
+    <row r="12" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>32</v>
       </c>
@@ -1832,7 +1836,7 @@
         <v>60.5</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="23.25" customHeight="1">
+    <row r="13" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>33</v>
       </c>
@@ -1909,7 +1913,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="23.25" customHeight="1">
+    <row r="14" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>34</v>
       </c>
@@ -1986,7 +1990,7 @@
         <v>61.2</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="23.25" customHeight="1">
+    <row r="15" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>35</v>
       </c>
@@ -2063,7 +2067,7 @@
         <v>61.1</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="23.25" customHeight="1">
+    <row r="16" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>36</v>
       </c>
@@ -2140,7 +2144,7 @@
         <v>61.1</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="23.25" customHeight="1">
+    <row r="17" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>37</v>
       </c>
@@ -2217,7 +2221,7 @@
         <v>61.1</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="23.25" customHeight="1">
+    <row r="18" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>38</v>
       </c>
@@ -2294,7 +2298,7 @@
         <v>61.1</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="23.25" customHeight="1">
+    <row r="19" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>39</v>
       </c>
@@ -2371,7 +2375,7 @@
         <v>60.8</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="23.25" customHeight="1">
+    <row r="20" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>40</v>
       </c>
@@ -2448,7 +2452,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="23.25" customHeight="1">
+    <row r="21" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>41</v>
       </c>
@@ -2525,7 +2529,7 @@
         <v>59.3</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="23.25" customHeight="1">
+    <row r="22" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>42</v>
       </c>
@@ -2602,7 +2606,7 @@
         <v>59.2</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="23.25" customHeight="1">
+    <row r="23" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>43</v>
       </c>
@@ -2679,7 +2683,7 @@
         <v>59.7</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="23.25" customHeight="1">
+    <row r="24" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>44</v>
       </c>
@@ -2756,7 +2760,7 @@
         <v>60.4</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="23.25" customHeight="1">
+    <row r="25" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>45</v>
       </c>
@@ -2833,7 +2837,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="23.25" customHeight="1">
+    <row r="26" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>46</v>
       </c>
@@ -2910,7 +2914,7 @@
         <v>61.2</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="23.25" customHeight="1">
+    <row r="27" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>47</v>
       </c>
@@ -2987,7 +2991,7 @@
         <v>61.3</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="23.25" customHeight="1">
+    <row r="28" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>48</v>
       </c>
@@ -3064,7 +3068,7 @@
         <v>61.2</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="23.25" customHeight="1">
+    <row r="29" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>49</v>
       </c>
@@ -3141,7 +3145,7 @@
         <v>61.2</v>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="23.25" customHeight="1">
+    <row r="30" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>50</v>
       </c>
@@ -3218,7 +3222,7 @@
         <v>61.2</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="23.25" customHeight="1">
+    <row r="31" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>51</v>
       </c>
@@ -3295,7 +3299,7 @@
         <v>60.9</v>
       </c>
     </row>
-    <row r="32" spans="1:25" ht="23.25" customHeight="1">
+    <row r="32" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>52</v>
       </c>
@@ -3372,7 +3376,7 @@
         <v>60.2</v>
       </c>
     </row>
-    <row r="33" spans="1:25" ht="23.25" customHeight="1">
+    <row r="33" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>53</v>
       </c>
@@ -3449,7 +3453,7 @@
         <v>59.5</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="23.25" customHeight="1">
+    <row r="34" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>54</v>
       </c>
@@ -3526,7 +3530,7 @@
         <v>59.6</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="23.25" customHeight="1">
+    <row r="35" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>55</v>
       </c>
@@ -3603,7 +3607,7 @@
         <v>60.2</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="23.25" customHeight="1">
+    <row r="36" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>56</v>
       </c>
@@ -3680,7 +3684,7 @@
         <v>60.9</v>
       </c>
     </row>
-    <row r="37" spans="1:25" ht="23.25" customHeight="1">
+    <row r="37" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>57</v>
       </c>
@@ -3757,7 +3761,7 @@
         <v>61.3</v>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="23.25" customHeight="1">
+    <row r="38" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>58</v>
       </c>
@@ -3834,7 +3838,7 @@
         <v>61.5</v>
       </c>
     </row>
-    <row r="39" spans="1:25" ht="23.25" customHeight="1">
+    <row r="39" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>59</v>
       </c>
@@ -3911,7 +3915,7 @@
         <v>61.4</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="23.25" customHeight="1">
+    <row r="40" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>60</v>
       </c>
@@ -3988,7 +3992,7 @@
         <v>61.4</v>
       </c>
     </row>
-    <row r="41" spans="1:25" ht="23.25" customHeight="1">
+    <row r="41" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>61</v>
       </c>
@@ -4065,7 +4069,7 @@
         <v>61.3</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="23.25" customHeight="1">
+    <row r="42" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>62</v>
       </c>
@@ -4142,7 +4146,7 @@
         <v>61.4</v>
       </c>
     </row>
-    <row r="43" spans="1:25" ht="23.25" customHeight="1">
+    <row r="43" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>63</v>
       </c>
@@ -4219,7 +4223,7 @@
         <v>61.1</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="23.25" customHeight="1">
+    <row r="44" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>64</v>
       </c>
@@ -4296,7 +4300,7 @@
         <v>60.4</v>
       </c>
     </row>
-    <row r="45" spans="1:25" ht="23.25" customHeight="1">
+    <row r="45" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>65</v>
       </c>
@@ -4373,7 +4377,7 @@
         <v>59.7</v>
       </c>
     </row>
-    <row r="46" spans="1:25" ht="23.25" customHeight="1">
+    <row r="46" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>66</v>
       </c>
@@ -4450,7 +4454,7 @@
         <v>59.6</v>
       </c>
     </row>
-    <row r="47" spans="1:25" ht="23.25" customHeight="1">
+    <row r="47" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>67</v>
       </c>
@@ -4527,7 +4531,7 @@
         <v>60.1</v>
       </c>
     </row>
-    <row r="48" spans="1:25" ht="23.25" customHeight="1">
+    <row r="48" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>68</v>
       </c>
@@ -4604,7 +4608,7 @@
         <v>60.8</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="23.25" customHeight="1">
+    <row r="49" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>69</v>
       </c>
@@ -4681,7 +4685,7 @@
         <v>61.2</v>
       </c>
     </row>
-    <row r="50" spans="1:25" ht="23.25" customHeight="1">
+    <row r="50" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>70</v>
       </c>
@@ -4758,7 +4762,7 @@
         <v>61.3</v>
       </c>
     </row>
-    <row r="51" spans="1:25" ht="23.25" customHeight="1">
+    <row r="51" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>71</v>
       </c>
@@ -4835,7 +4839,7 @@
         <v>61.2</v>
       </c>
     </row>
-    <row r="52" spans="1:25" ht="23.25" customHeight="1">
+    <row r="52" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>72</v>
       </c>
@@ -4912,7 +4916,7 @@
         <v>61.1</v>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="23.25" customHeight="1">
+    <row r="53" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>73</v>
       </c>
@@ -4989,7 +4993,7 @@
         <v>61.1</v>
       </c>
     </row>
-    <row r="54" spans="1:25" ht="23.25" customHeight="1">
+    <row r="54" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>74</v>
       </c>
@@ -5066,7 +5070,7 @@
         <v>61.3</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="23.25" customHeight="1">
+    <row r="55" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>75</v>
       </c>
@@ -5143,7 +5147,7 @@
         <v>60.9</v>
       </c>
     </row>
-    <row r="56" spans="1:25" ht="23.25" customHeight="1">
+    <row r="56" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>76</v>
       </c>
@@ -5220,7 +5224,7 @@
         <v>60.2</v>
       </c>
     </row>
-    <row r="57" spans="1:25" ht="23.25" customHeight="1">
+    <row r="57" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>77</v>
       </c>
@@ -5297,7 +5301,7 @@
         <v>59.6</v>
       </c>
     </row>
-    <row r="58" spans="1:25" ht="23.25" customHeight="1">
+    <row r="58" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>78</v>
       </c>
@@ -5374,7 +5378,7 @@
         <v>59.7</v>
       </c>
     </row>
-    <row r="59" spans="1:25" ht="23.25" customHeight="1">
+    <row r="59" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>79</v>
       </c>
@@ -5451,7 +5455,7 @@
         <v>60.2</v>
       </c>
     </row>
-    <row r="60" spans="1:25" ht="23.25" customHeight="1">
+    <row r="60" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>80</v>
       </c>
@@ -5528,7 +5532,7 @@
         <v>60.9</v>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="23.25" customHeight="1">
+    <row r="61" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>81</v>
       </c>
@@ -5605,7 +5609,7 @@
         <v>61.3</v>
       </c>
     </row>
-    <row r="62" spans="1:25" ht="23.25" customHeight="1">
+    <row r="62" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>82</v>
       </c>
@@ -5682,7 +5686,7 @@
         <v>61.5</v>
       </c>
     </row>
-    <row r="63" spans="1:25" ht="23.25" customHeight="1">
+    <row r="63" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>83</v>
       </c>
@@ -5759,7 +5763,7 @@
         <v>61.5</v>
       </c>
     </row>
-    <row r="64" spans="1:25" ht="23.25" customHeight="1">
+    <row r="64" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>84</v>
       </c>
@@ -5836,7 +5840,7 @@
         <v>61.5</v>
       </c>
     </row>
-    <row r="65" spans="1:25" ht="23.25" customHeight="1">
+    <row r="65" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>85</v>
       </c>
@@ -5913,7 +5917,7 @@
         <v>61.5</v>
       </c>
     </row>
-    <row r="66" spans="1:25" ht="23.25" customHeight="1">
+    <row r="66" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>86</v>
       </c>
@@ -5990,7 +5994,7 @@
         <v>61.6</v>
       </c>
     </row>
-    <row r="67" spans="1:25" ht="23.25" customHeight="1">
+    <row r="67" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>87</v>
       </c>
@@ -6067,7 +6071,7 @@
         <v>61.4</v>
       </c>
     </row>
-    <row r="68" spans="1:25" ht="23.25" customHeight="1">
+    <row r="68" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>88</v>
       </c>
@@ -6144,7 +6148,7 @@
         <v>60.8</v>
       </c>
     </row>
-    <row r="69" spans="1:25" ht="23.25" customHeight="1">
+    <row r="69" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>89</v>
       </c>
@@ -6221,7 +6225,7 @@
         <v>60.3</v>
       </c>
     </row>
-    <row r="70" spans="1:25" ht="23.25" customHeight="1">
+    <row r="70" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>90</v>
       </c>
@@ -6298,7 +6302,7 @@
         <v>59.8</v>
       </c>
     </row>
-    <row r="71" spans="1:25" ht="23.25" customHeight="1">
+    <row r="71" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>91</v>
       </c>
@@ -6375,7 +6379,7 @@
         <v>59.6</v>
       </c>
     </row>
-    <row r="72" spans="1:25" ht="23.25" customHeight="1">
+    <row r="72" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>92</v>
       </c>
@@ -6452,7 +6456,7 @@
         <v>59.7</v>
       </c>
     </row>
-    <row r="73" spans="1:25" ht="23.25" customHeight="1">
+    <row r="73" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>93</v>
       </c>
@@ -6529,7 +6533,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="74" spans="1:25" ht="23.25" customHeight="1">
+    <row r="74" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>94</v>
       </c>
@@ -6606,7 +6610,7 @@
         <v>60.4</v>
       </c>
     </row>
-    <row r="75" spans="1:25" ht="23.25" customHeight="1">
+    <row r="75" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>95</v>
       </c>
@@ -6683,7 +6687,7 @@
         <v>60.4</v>
       </c>
     </row>
-    <row r="76" spans="1:25" ht="23.25" customHeight="1">
+    <row r="76" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>96</v>
       </c>
@@ -6760,7 +6764,7 @@
         <v>60.4</v>
       </c>
     </row>
-    <row r="77" spans="1:25" ht="23.25" customHeight="1">
+    <row r="77" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>97</v>
       </c>
@@ -6837,7 +6841,7 @@
         <v>60.4</v>
       </c>
     </row>
-    <row r="78" spans="1:25" ht="23.25" customHeight="1">
+    <row r="78" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>98</v>
       </c>
@@ -6914,7 +6918,7 @@
         <v>60.5</v>
       </c>
     </row>
-    <row r="79" spans="1:25" ht="23.25" customHeight="1">
+    <row r="79" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>99</v>
       </c>
@@ -6991,7 +6995,7 @@
         <v>60.1</v>
       </c>
     </row>
-    <row r="80" spans="1:25" ht="23.25" customHeight="1">
+    <row r="80" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>100</v>
       </c>
@@ -7068,7 +7072,7 @@
         <v>59.1</v>
       </c>
     </row>
-    <row r="81" spans="1:25" ht="23.25" customHeight="1">
+    <row r="81" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>101</v>
       </c>
@@ -7145,7 +7149,7 @@
         <v>58.4</v>
       </c>
     </row>
-    <row r="82" spans="1:25" ht="23.25" customHeight="1">
+    <row r="82" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>102</v>
       </c>
@@ -7222,7 +7226,7 @@
         <v>58.6</v>
       </c>
     </row>
-    <row r="83" spans="1:25" ht="23.25" customHeight="1">
+    <row r="83" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>103</v>
       </c>
@@ -7299,7 +7303,7 @@
         <v>59.6</v>
       </c>
     </row>
-    <row r="84" spans="1:25" ht="23.25" customHeight="1">
+    <row r="84" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>104</v>
       </c>
@@ -7376,7 +7380,7 @@
         <v>60.5</v>
       </c>
     </row>
-    <row r="85" spans="1:25" ht="23.25" customHeight="1">
+    <row r="85" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>105</v>
       </c>
@@ -7453,7 +7457,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="86" spans="1:25" ht="23.25" customHeight="1">
+    <row r="86" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>106</v>
       </c>
@@ -7530,7 +7534,7 @@
         <v>61.3</v>
       </c>
     </row>
-    <row r="87" spans="1:25" ht="23.25" customHeight="1">
+    <row r="87" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>107</v>
       </c>
@@ -7607,7 +7611,7 @@
         <v>61.3</v>
       </c>
     </row>
-    <row r="88" spans="1:25" ht="23.25" customHeight="1">
+    <row r="88" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>108</v>
       </c>
@@ -7684,7 +7688,7 @@
         <v>61.3</v>
       </c>
     </row>
-    <row r="89" spans="1:25" ht="23.25" customHeight="1">
+    <row r="89" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>109</v>
       </c>
@@ -7761,7 +7765,7 @@
         <v>61.3</v>
       </c>
     </row>
-    <row r="90" spans="1:25" ht="23.25" customHeight="1">
+    <row r="90" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>110</v>
       </c>
@@ -7838,7 +7842,7 @@
         <v>61.4</v>
       </c>
     </row>
-    <row r="91" spans="1:25" ht="23.25" customHeight="1">
+    <row r="91" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>111</v>
       </c>
@@ -7915,7 +7919,7 @@
         <v>61.1</v>
       </c>
     </row>
-    <row r="92" spans="1:25" ht="23.25" customHeight="1">
+    <row r="92" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>112</v>
       </c>
@@ -7992,7 +7996,7 @@
         <v>60.5</v>
       </c>
     </row>
-    <row r="93" spans="1:25" ht="23.25" customHeight="1">
+    <row r="93" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>113</v>
       </c>
@@ -8069,7 +8073,7 @@
         <v>60.2</v>
       </c>
     </row>
-    <row r="94" spans="1:25" ht="23.25" customHeight="1">
+    <row r="94" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>114</v>
       </c>
@@ -8146,7 +8150,7 @@
         <v>60.5</v>
       </c>
     </row>
-    <row r="95" spans="1:25" ht="23.25" customHeight="1">
+    <row r="95" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>115</v>
       </c>
@@ -8223,7 +8227,7 @@
         <v>61.4</v>
       </c>
     </row>
-    <row r="96" spans="1:25" ht="23.25" customHeight="1">
+    <row r="96" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>116</v>
       </c>
@@ -8300,7 +8304,7 @@
         <v>62.2</v>
       </c>
     </row>
-    <row r="97" spans="1:25" ht="23.25" customHeight="1">
+    <row r="97" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>117</v>
       </c>
@@ -8377,7 +8381,7 @@
         <v>62.7</v>
       </c>
     </row>
-    <row r="98" spans="1:25" ht="23.25" customHeight="1">
+    <row r="98" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>118</v>
       </c>
@@ -8454,7 +8458,7 @@
         <v>62.9</v>
       </c>
     </row>
-    <row r="99" spans="1:25" ht="23.25" customHeight="1">
+    <row r="99" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>119</v>
       </c>
@@ -8531,7 +8535,7 @@
         <v>62.9</v>
       </c>
     </row>
-    <row r="100" spans="1:25" ht="23.25" customHeight="1">
+    <row r="100" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>120</v>
       </c>
@@ -8608,7 +8612,7 @@
         <v>62.8</v>
       </c>
     </row>
-    <row r="101" spans="1:25" ht="23.25" customHeight="1">
+    <row r="101" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>121</v>
       </c>
@@ -8685,7 +8689,7 @@
         <v>62.7</v>
       </c>
     </row>
-    <row r="102" spans="1:25" ht="23.25" customHeight="1">
+    <row r="102" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>122</v>
       </c>
@@ -8762,7 +8766,7 @@
         <v>62.7</v>
       </c>
     </row>
-    <row r="103" spans="1:25" ht="23.25" customHeight="1">
+    <row r="103" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>123</v>
       </c>
@@ -8839,7 +8843,7 @@
         <v>62.2</v>
       </c>
     </row>
-    <row r="104" spans="1:25" ht="23.25" customHeight="1">
+    <row r="104" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>124</v>
       </c>
@@ -8916,7 +8920,7 @@
         <v>61.4</v>
       </c>
     </row>
-    <row r="105" spans="1:25" ht="23.25" customHeight="1">
+    <row r="105" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>125</v>
       </c>
@@ -8993,7 +8997,7 @@
         <v>60.9</v>
       </c>
     </row>
-    <row r="106" spans="1:25" ht="23.25" customHeight="1">
+    <row r="106" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>126</v>
       </c>
@@ -9070,7 +9074,7 @@
         <v>61.2</v>
       </c>
     </row>
-    <row r="107" spans="1:25" ht="23.25" customHeight="1">
+    <row r="107" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>127</v>
       </c>
@@ -9147,7 +9151,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="108" spans="1:25" ht="23.25" customHeight="1">
+    <row r="108" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>128</v>
       </c>
@@ -9224,7 +9228,7 @@
         <v>62.8</v>
       </c>
     </row>
-    <row r="109" spans="1:25" ht="23.25" customHeight="1">
+    <row r="109" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>129</v>
       </c>
@@ -9301,7 +9305,7 @@
         <v>63.2</v>
       </c>
     </row>
-    <row r="110" spans="1:25" ht="23.25" customHeight="1">
+    <row r="110" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>130</v>
       </c>
@@ -9378,7 +9382,7 @@
         <v>63.4</v>
       </c>
     </row>
-    <row r="111" spans="1:25" ht="23.25" customHeight="1">
+    <row r="111" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>131</v>
       </c>
@@ -9455,7 +9459,7 @@
         <v>63.3</v>
       </c>
     </row>
-    <row r="112" spans="1:25" ht="23.25" customHeight="1">
+    <row r="112" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>132</v>
       </c>
@@ -9532,7 +9536,7 @@
         <v>63.2</v>
       </c>
     </row>
-    <row r="113" spans="1:25" ht="23.25" customHeight="1">
+    <row r="113" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>133</v>
       </c>
@@ -9609,7 +9613,7 @@
         <v>63.2</v>
       </c>
     </row>
-    <row r="114" spans="1:25" ht="23.25" customHeight="1">
+    <row r="114" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>134</v>
       </c>
@@ -9686,7 +9690,7 @@
         <v>63.2</v>
       </c>
     </row>
-    <row r="115" spans="1:25" ht="23.25" customHeight="1">
+    <row r="115" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>135</v>
       </c>
@@ -9763,7 +9767,7 @@
         <v>62.7</v>
       </c>
     </row>
-    <row r="116" spans="1:25" ht="23.25" customHeight="1">
+    <row r="116" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>136</v>
       </c>
@@ -9840,7 +9844,7 @@
         <v>61.9</v>
       </c>
     </row>
-    <row r="117" spans="1:25" ht="23.25" customHeight="1">
+    <row r="117" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>137</v>
       </c>
@@ -9917,7 +9921,7 @@
         <v>61.4</v>
       </c>
     </row>
-    <row r="118" spans="1:25" ht="23.25" customHeight="1">
+    <row r="118" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>138</v>
       </c>
@@ -9994,7 +9998,7 @@
         <v>61.7</v>
       </c>
     </row>
-    <row r="119" spans="1:25" ht="23.25" customHeight="1">
+    <row r="119" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>139</v>
       </c>
@@ -10071,226 +10075,226 @@
         <v>62.3</v>
       </c>
     </row>
-    <row r="120" spans="1:25" ht="23.25" customHeight="1">
+    <row r="120" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>140</v>
       </c>
       <c r="B120" s="3">
-        <v>29578</v>
+        <v>0</v>
       </c>
       <c r="C120" s="3">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="D120" s="3">
-        <v>342</v>
+        <v>0</v>
       </c>
       <c r="E120" s="3">
-        <v>29555</v>
+        <v>0</v>
       </c>
       <c r="F120" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G120" s="3">
         <v>0</v>
       </c>
       <c r="H120" s="3">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I120" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J120" s="3">
-        <v>45539</v>
+        <v>0</v>
       </c>
       <c r="K120" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L120" s="3">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="M120" s="3">
-        <v>45537</v>
+        <v>0</v>
       </c>
       <c r="N120" s="3">
-        <v>15961</v>
+        <v>0</v>
       </c>
       <c r="O120" s="3">
-        <v>-281</v>
+        <v>0</v>
       </c>
       <c r="P120" s="3">
-        <v>-174</v>
+        <v>0</v>
       </c>
       <c r="Q120" s="3">
-        <v>15982</v>
+        <v>0</v>
       </c>
       <c r="R120" s="3">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="S120" s="3">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="T120" s="3">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="U120" s="3">
-        <v>64.900000000000006</v>
+        <v>0</v>
       </c>
       <c r="V120" s="3">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="W120" s="3">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="X120" s="3">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="Y120" s="3">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="121" spans="1:25" ht="23.25" customHeight="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B121" s="3">
-        <v>29799</v>
+        <v>0</v>
       </c>
       <c r="C121" s="3">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="D121" s="3">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="E121" s="3">
-        <v>29714</v>
+        <v>0</v>
       </c>
       <c r="F121" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G121" s="3">
         <v>0</v>
       </c>
       <c r="H121" s="3">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I121" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J121" s="3">
-        <v>45543</v>
+        <v>0</v>
       </c>
       <c r="K121" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L121" s="3">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="M121" s="3">
-        <v>45544</v>
+        <v>0</v>
       </c>
       <c r="N121" s="3">
-        <v>15744</v>
+        <v>0</v>
       </c>
       <c r="O121" s="3">
-        <v>-217</v>
+        <v>0</v>
       </c>
       <c r="P121" s="3">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="Q121" s="3">
-        <v>15830</v>
+        <v>0</v>
       </c>
       <c r="R121" s="3">
-        <v>65.400000000000006</v>
+        <v>0</v>
       </c>
       <c r="S121" s="3">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="T121" s="3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="U121" s="3">
-        <v>65.2</v>
+        <v>0</v>
       </c>
       <c r="V121" s="3">
-        <v>63.5</v>
+        <v>0</v>
       </c>
       <c r="W121" s="3">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X121" s="3">
         <v>0</v>
       </c>
       <c r="Y121" s="3">
-        <v>63.3</v>
-      </c>
-    </row>
-    <row r="122" spans="1:25" ht="23.25" customHeight="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>142</v>
       </c>
       <c r="B122" s="3">
-        <v>29764</v>
+        <v>0</v>
       </c>
       <c r="C122" s="3">
-        <v>-35</v>
+        <v>0</v>
       </c>
       <c r="D122" s="3">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="E122" s="3">
-        <v>29719</v>
+        <v>0</v>
       </c>
       <c r="F122" s="3">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="G122" s="3">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="H122" s="3">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I122" s="3">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="J122" s="3">
-        <v>45550</v>
+        <v>0</v>
       </c>
       <c r="K122" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L122" s="3">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="M122" s="3">
-        <v>45561</v>
+        <v>0</v>
       </c>
       <c r="N122" s="3">
-        <v>15786</v>
+        <v>0</v>
       </c>
       <c r="O122" s="3">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="P122" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Q122" s="3">
-        <v>15842</v>
+        <v>0</v>
       </c>
       <c r="R122" s="3">
-        <v>65.3</v>
+        <v>0</v>
       </c>
       <c r="S122" s="3">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="T122" s="3">
         <v>0</v>
       </c>
       <c r="U122" s="3">
-        <v>65.2</v>
+        <v>0</v>
       </c>
       <c r="V122" s="3">
-        <v>63.5</v>
+        <v>0</v>
       </c>
       <c r="W122" s="3">
         <v>0</v>
@@ -10299,306 +10303,306 @@
         <v>0</v>
       </c>
       <c r="Y122" s="3">
-        <v>63.4</v>
-      </c>
-    </row>
-    <row r="123" spans="1:25" ht="23.25" customHeight="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>143</v>
       </c>
       <c r="B123" s="3">
-        <v>29594</v>
+        <v>0</v>
       </c>
       <c r="C123" s="3">
-        <v>-170</v>
+        <v>0</v>
       </c>
       <c r="D123" s="3">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="E123" s="3">
-        <v>29574</v>
+        <v>0</v>
       </c>
       <c r="F123" s="3">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="G123" s="3">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="H123" s="3">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="I123" s="3">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="J123" s="3">
-        <v>45590</v>
+        <v>0</v>
       </c>
       <c r="K123" s="3">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L123" s="3">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="M123" s="3">
-        <v>45572</v>
+        <v>0</v>
       </c>
       <c r="N123" s="3">
-        <v>15996</v>
+        <v>0</v>
       </c>
       <c r="O123" s="3">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="P123" s="3">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="Q123" s="3">
-        <v>15998</v>
+        <v>0</v>
       </c>
       <c r="R123" s="3">
-        <v>64.900000000000006</v>
+        <v>0</v>
       </c>
       <c r="S123" s="3">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="T123" s="3">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="U123" s="3">
-        <v>64.900000000000006</v>
+        <v>0</v>
       </c>
       <c r="V123" s="3">
-        <v>63.3</v>
+        <v>0</v>
       </c>
       <c r="W123" s="3">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="X123" s="3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Y123" s="3">
-        <v>63.3</v>
-      </c>
-    </row>
-    <row r="124" spans="1:25" ht="23.25" customHeight="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>144</v>
       </c>
       <c r="B124" s="3">
-        <v>29365</v>
+        <v>0</v>
       </c>
       <c r="C124" s="3">
-        <v>-229</v>
+        <v>0</v>
       </c>
       <c r="D124" s="3">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="E124" s="3">
-        <v>29474</v>
+        <v>0</v>
       </c>
       <c r="F124" s="3">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="G124" s="3">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="H124" s="3">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="I124" s="3">
-        <v>2.2000000000000002</v>
+        <v>0</v>
       </c>
       <c r="J124" s="3">
-        <v>45576</v>
+        <v>0</v>
       </c>
       <c r="K124" s="3">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="L124" s="3">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="M124" s="3">
-        <v>45585</v>
+        <v>0</v>
       </c>
       <c r="N124" s="3">
-        <v>16211</v>
+        <v>0</v>
       </c>
       <c r="O124" s="3">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="P124" s="3">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="Q124" s="3">
-        <v>16111</v>
+        <v>0</v>
       </c>
       <c r="R124" s="3">
-        <v>64.400000000000006</v>
+        <v>0</v>
       </c>
       <c r="S124" s="3">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="T124" s="3">
         <v>0</v>
       </c>
       <c r="U124" s="3">
-        <v>64.599999999999994</v>
+        <v>0</v>
       </c>
       <c r="V124" s="3">
-        <v>63.2</v>
+        <v>0</v>
       </c>
       <c r="W124" s="3">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="X124" s="3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Y124" s="3">
-        <v>63.3</v>
-      </c>
-    </row>
-    <row r="125" spans="1:25" ht="23.25" customHeight="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>145</v>
       </c>
       <c r="B125" s="3">
-        <v>29464</v>
+        <v>0</v>
       </c>
       <c r="C125" s="3">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="D125" s="3">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="E125" s="3">
-        <v>29451</v>
+        <v>0</v>
       </c>
       <c r="F125" s="3">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="G125" s="3">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H125" s="3">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="I125" s="3">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="J125" s="3">
-        <v>45590</v>
+        <v>0</v>
       </c>
       <c r="K125" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L125" s="3">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="M125" s="3">
-        <v>45591</v>
+        <v>0</v>
       </c>
       <c r="N125" s="3">
-        <v>16125</v>
+        <v>0</v>
       </c>
       <c r="O125" s="3">
-        <v>-86</v>
+        <v>0</v>
       </c>
       <c r="P125" s="3">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="Q125" s="3">
-        <v>16139</v>
+        <v>0</v>
       </c>
       <c r="R125" s="3">
-        <v>64.599999999999994</v>
+        <v>0</v>
       </c>
       <c r="S125" s="3">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="T125" s="3">
         <v>0</v>
       </c>
       <c r="U125" s="3">
-        <v>64.599999999999994</v>
+        <v>0</v>
       </c>
       <c r="V125" s="3">
-        <v>63.3</v>
+        <v>0</v>
       </c>
       <c r="W125" s="3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="X125" s="3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Y125" s="3">
-        <v>63.3</v>
-      </c>
-    </row>
-    <row r="126" spans="1:25" ht="23.25" customHeight="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>146</v>
       </c>
       <c r="B126" s="3">
-        <v>29525</v>
+        <v>0</v>
       </c>
       <c r="C126" s="3">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="D126" s="3">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="E126" s="3">
-        <v>29489</v>
+        <v>0</v>
       </c>
       <c r="F126" s="3">
-        <v>2.2999999999999998</v>
+        <v>0</v>
       </c>
       <c r="G126" s="3">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H126" s="3">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I126" s="3">
-        <v>2.2000000000000002</v>
+        <v>0</v>
       </c>
       <c r="J126" s="3">
-        <v>45607</v>
+        <v>0</v>
       </c>
       <c r="K126" s="3">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L126" s="3">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="M126" s="3">
-        <v>45608</v>
+        <v>0</v>
       </c>
       <c r="N126" s="3">
-        <v>16082</v>
+        <v>0</v>
       </c>
       <c r="O126" s="3">
-        <v>-43</v>
+        <v>0</v>
       </c>
       <c r="P126" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q126" s="3">
-        <v>16119</v>
+        <v>0</v>
       </c>
       <c r="R126" s="3">
-        <v>64.7</v>
+        <v>0</v>
       </c>
       <c r="S126" s="3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="T126" s="3">
         <v>0</v>
       </c>
       <c r="U126" s="3">
-        <v>64.599999999999994</v>
+        <v>0</v>
       </c>
       <c r="V126" s="3">
-        <v>63.3</v>
+        <v>0</v>
       </c>
       <c r="W126" s="3">
         <v>0</v>
@@ -10607,319 +10611,330 @@
         <v>0</v>
       </c>
       <c r="Y126" s="3">
-        <v>63.3</v>
-      </c>
-    </row>
-    <row r="127" spans="1:25" ht="23.25" customHeight="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>147</v>
       </c>
       <c r="B127" s="3">
-        <v>29477</v>
+        <v>0</v>
       </c>
       <c r="C127" s="3">
-        <v>-48</v>
+        <v>0</v>
       </c>
       <c r="D127" s="3">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="E127" s="3">
-        <v>29386</v>
+        <v>0</v>
       </c>
       <c r="F127" s="3">
-        <v>2.2000000000000002</v>
+        <v>0</v>
       </c>
       <c r="G127" s="3">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="H127" s="3">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="I127" s="3">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="J127" s="3">
-        <v>45628</v>
+        <v>0</v>
       </c>
       <c r="K127" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L127" s="3">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="M127" s="3">
-        <v>45629</v>
+        <v>0</v>
       </c>
       <c r="N127" s="3">
-        <v>16151</v>
+        <v>0</v>
       </c>
       <c r="O127" s="3">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="P127" s="3">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="Q127" s="3">
-        <v>16244</v>
+        <v>0</v>
       </c>
       <c r="R127" s="3">
-        <v>64.599999999999994</v>
+        <v>0</v>
       </c>
       <c r="S127" s="3">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="T127" s="3">
         <v>0</v>
       </c>
       <c r="U127" s="3">
-        <v>64.400000000000006</v>
+        <v>0</v>
       </c>
       <c r="V127" s="3">
-        <v>63.2</v>
+        <v>0</v>
       </c>
       <c r="W127" s="3">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="X127" s="3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Y127" s="3">
-        <v>62.6</v>
-      </c>
-    </row>
-    <row r="128" spans="1:25" ht="23.25" customHeight="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>148</v>
       </c>
       <c r="B128" s="3">
-        <v>29156</v>
+        <v>0</v>
       </c>
       <c r="C128" s="3">
-        <v>-321</v>
+        <v>0</v>
       </c>
       <c r="D128" s="3">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="E128" s="3">
-        <v>29198</v>
+        <v>0</v>
       </c>
       <c r="F128" s="3">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="G128" s="3">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="H128" s="3">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I128" s="3">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="J128" s="3">
-        <v>45653</v>
+        <v>0</v>
       </c>
       <c r="K128" s="3">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L128" s="3">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="M128" s="3">
-        <v>45652</v>
+        <v>0</v>
       </c>
       <c r="N128" s="3">
-        <v>16498</v>
+        <v>0</v>
       </c>
       <c r="O128" s="3">
-        <v>347</v>
+        <v>0</v>
       </c>
       <c r="P128" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q128" s="3">
-        <v>16454</v>
+        <v>0</v>
       </c>
       <c r="R128" s="3">
-        <v>63.9</v>
+        <v>0</v>
       </c>
       <c r="S128" s="3">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
       <c r="T128" s="3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="U128" s="3">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="V128" s="3">
-        <v>61.4</v>
+        <v>0</v>
       </c>
       <c r="W128" s="3">
-        <v>-1.8</v>
+        <v>0</v>
       </c>
       <c r="X128" s="3">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="Y128" s="3">
-        <v>61.9</v>
-      </c>
-    </row>
-    <row r="129" spans="1:25" ht="23.25" customHeight="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>149</v>
       </c>
       <c r="B129" s="3">
-        <v>28961</v>
+        <v>0</v>
       </c>
       <c r="C129" s="3">
-        <v>-195</v>
+        <v>0</v>
       </c>
       <c r="D129" s="3">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="E129" s="3">
-        <v>29079</v>
+        <v>0</v>
       </c>
       <c r="F129" s="3">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="G129" s="3">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="H129" s="3">
         <v>0</v>
       </c>
       <c r="I129" s="3">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="J129" s="3">
-        <v>45674</v>
+        <v>0</v>
       </c>
       <c r="K129" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L129" s="3">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="M129" s="3">
-        <v>45674</v>
+        <v>0</v>
       </c>
       <c r="N129" s="3">
-        <v>16713</v>
+        <v>0</v>
       </c>
       <c r="O129" s="3">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="P129" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q129" s="3">
-        <v>16595</v>
+        <v>0</v>
       </c>
       <c r="R129" s="3">
-        <v>63.4</v>
+        <v>0</v>
       </c>
       <c r="S129" s="3">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="T129" s="3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="U129" s="3">
-        <v>63.7</v>
+        <v>0</v>
       </c>
       <c r="V129" s="3">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="W129" s="3">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="X129" s="3">
         <v>0</v>
       </c>
       <c r="Y129" s="3">
-        <v>61.4</v>
-      </c>
-    </row>
-    <row r="130" spans="1:25" ht="23.25" customHeight="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>150</v>
       </c>
       <c r="B130" s="3">
-        <v>29119</v>
+        <v>0</v>
       </c>
       <c r="C130" s="3">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="D130" s="3">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="E130" s="3">
-        <v>29040</v>
+        <v>0</v>
       </c>
       <c r="F130" s="3">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="G130" s="3">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="H130" s="3">
         <v>0</v>
       </c>
       <c r="I130" s="3">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="J130" s="3">
-        <v>45694</v>
+        <v>0</v>
       </c>
       <c r="K130" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L130" s="3">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="M130" s="3">
-        <v>45684</v>
+        <v>0</v>
       </c>
       <c r="N130" s="3">
-        <v>16575</v>
+        <v>0</v>
       </c>
       <c r="O130" s="3">
-        <v>-138</v>
+        <v>0</v>
       </c>
       <c r="P130" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q130" s="3">
-        <v>16644</v>
+        <v>0</v>
       </c>
       <c r="R130" s="3">
-        <v>63.7</v>
+        <v>0</v>
       </c>
       <c r="S130" s="3">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="T130" s="3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="U130" s="3">
-        <v>63.6</v>
+        <v>0</v>
       </c>
       <c r="V130" s="3">
-        <v>61.7</v>
+        <v>0</v>
       </c>
       <c r="W130" s="3">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="X130" s="3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Y130" s="3">
-        <v>61.4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="V5:Y5"/>
+    <mergeCell ref="V2:Y2"/>
+    <mergeCell ref="R2:U2"/>
+    <mergeCell ref="N2:Q2"/>
+    <mergeCell ref="J2:M2"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="J5:M5"/>
+    <mergeCell ref="N5:Q5"/>
+    <mergeCell ref="R5:U5"/>
     <mergeCell ref="B1:Y1"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="F4:I4"/>
@@ -10934,17 +10949,6 @@
     <mergeCell ref="J3:M3"/>
     <mergeCell ref="N3:Q3"/>
     <mergeCell ref="R3:U3"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="J5:M5"/>
-    <mergeCell ref="N5:Q5"/>
-    <mergeCell ref="R5:U5"/>
-    <mergeCell ref="V5:Y5"/>
-    <mergeCell ref="V2:Y2"/>
-    <mergeCell ref="R2:U2"/>
-    <mergeCell ref="N2:Q2"/>
-    <mergeCell ref="J2:M2"/>
-    <mergeCell ref="V3:Y3"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10954,206 +10958,206 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A41"/>
-  <sheetFormatPr defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="196"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="23.25" customHeight="1">
+    <row r="1" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="23.25" customHeight="1">
+    <row r="2" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="23.25" customHeight="1">
+    <row r="3" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="23.25" customHeight="1">
+    <row r="4" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="23.25" customHeight="1">
+    <row r="5" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="23.25" customHeight="1">
+    <row r="6" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="23.25" customHeight="1">
+    <row r="7" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
     </row>
-    <row r="8" spans="1:1" ht="23.25" customHeight="1">
+    <row r="8" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
     </row>
-    <row r="9" spans="1:1" ht="23.25" customHeight="1">
+    <row r="9" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="23.25" customHeight="1">
+    <row r="10" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="23.25" customHeight="1">
+    <row r="11" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="23.25" customHeight="1">
+    <row r="12" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="23.25" customHeight="1">
+    <row r="13" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="23.25" customHeight="1">
+    <row r="14" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="23.25" customHeight="1">
+    <row r="15" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="23.25" customHeight="1">
+    <row r="16" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="23.25" customHeight="1">
+    <row r="17" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="23.25" customHeight="1">
+    <row r="18" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="23.25" customHeight="1">
+    <row r="19" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="23.25" customHeight="1">
+    <row r="20" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="23.25" customHeight="1">
+    <row r="21" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="23.25" customHeight="1">
+    <row r="22" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="23" spans="1:1" ht="23.25" customHeight="1">
+    <row r="23" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="24" spans="1:1" ht="23.25" customHeight="1">
+    <row r="24" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="25" spans="1:1" ht="23.25" customHeight="1">
+    <row r="25" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="26" spans="1:1" ht="23.25" customHeight="1">
+    <row r="26" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="27" spans="1:1" ht="23.25" customHeight="1">
+    <row r="27" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="28" spans="1:1" ht="23.25" customHeight="1">
+    <row r="28" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="29" spans="1:1" ht="23.25" customHeight="1">
+    <row r="29" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="30" spans="1:1" ht="23.25" customHeight="1">
+    <row r="30" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="31" spans="1:1" ht="23.25" customHeight="1">
+    <row r="31" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="32" spans="1:1" ht="23.25" customHeight="1">
+    <row r="32" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="33" spans="1:1" ht="23.25" customHeight="1">
+    <row r="33" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="34" spans="1:1" ht="23.25" customHeight="1">
+    <row r="34" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="35" spans="1:1" ht="23.25" customHeight="1">
+    <row r="35" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="36" spans="1:1" ht="23.25" customHeight="1">
+    <row r="36" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="37" spans="1:1" ht="23.25" customHeight="1">
+    <row r="37" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4"/>
     </row>
-    <row r="38" spans="1:1" ht="23.25" customHeight="1">
+    <row r="38" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="39" spans="1:1" ht="23.25" customHeight="1">
+    <row r="39" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="40" spans="1:1" ht="23.25" customHeight="1">
+    <row r="40" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="41" spans="1:1" ht="23.25" customHeight="1">
+    <row r="41" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
     </row>
   </sheetData>
